--- a/p6_deployment/data/usa/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/p6_deployment/data/usa/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D85"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,1436 +448,1848 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>AkMS0VKH</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="C2" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="D2" t="n">
-        <v>4.5</v>
+          <t>tflZ7nSp</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>hEBXakzO</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="C3" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D3" t="n">
-        <v>2.55</v>
+          <t>raSHWV4o</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>6HFya9kU</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C4" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="D4" t="n">
-        <v>6</v>
+          <t>zg5jGAK4</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>WbNO1B5B</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="C5" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="D5" t="n">
-        <v>5.5</v>
+          <t>ld9fFUZA</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>2PIK2ij5</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="C6" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D6" t="n">
-        <v>2.9</v>
+          <t>WKbaElkH</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>lIfIy3Ui</t>
-        </is>
-      </c>
-      <c r="B7" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="C7" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="D7" t="n">
-        <v>3</v>
+          <t>ABc3D84N</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>UZQ75g6n</t>
-        </is>
-      </c>
-      <c r="B8" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="C8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D8" t="n">
-        <v>2</v>
+          <t>vo27CSJT</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>6gkNzNqb</t>
-        </is>
-      </c>
-      <c r="B9" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="C9" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="D9" t="n">
-        <v>3.9</v>
+          <t>MTkoJCzn</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>tAUB4DLh</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="C10" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D10" t="n">
-        <v>3.1</v>
+          <t>hK8xvrmh</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>pplRZta4</t>
-        </is>
-      </c>
-      <c r="B11" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="C11" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D11" t="n">
-        <v>4.1</v>
+          <t>rwisKhLu</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>v7mVY0EA</t>
-        </is>
-      </c>
-      <c r="B12" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="C12" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D12" t="n">
-        <v>2.6</v>
+          <t>2u7rIWkh</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>OYJG3Xza</t>
-        </is>
-      </c>
-      <c r="B13" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="C13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="D13" t="n">
-        <v>3.6</v>
+          <t>tW5nHj5b</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>bc9YvOXo</t>
-        </is>
-      </c>
-      <c r="B14" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="C14" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D14" t="n">
-        <v>3.8</v>
+          <t>WA7tw22b</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>AReExqFo</t>
-        </is>
-      </c>
-      <c r="B15" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="C15" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D15" t="n">
-        <v>3.1</v>
+          <t>AkMS0VKH</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>nFu3VR7I</t>
-        </is>
-      </c>
-      <c r="B16" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="C16" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D16" t="n">
-        <v>3.1</v>
+          <t>hEBXakzO</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>4jjbW7hC</t>
-        </is>
-      </c>
-      <c r="B17" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="C17" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="D17" t="n">
-        <v>2.8</v>
+          <t>6HFya9kU</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>6.00</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>dO7WDaxo</t>
-        </is>
-      </c>
-      <c r="B18" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="C18" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D18" t="n">
-        <v>4.5</v>
+          <t>WbNO1B5B</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1.60</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>QaifXmw6</t>
-        </is>
-      </c>
-      <c r="B19" t="n">
-        <v>2.55</v>
-      </c>
-      <c r="C19" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D19" t="n">
-        <v>2.6</v>
+          <t>2PIK2ij5</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>dQnjYTNa</t>
-        </is>
-      </c>
-      <c r="B20" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="C20" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D20" t="n">
-        <v>4.2</v>
+          <t>lIfIy3Ui</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>zBbszjgm</t>
-        </is>
-      </c>
-      <c r="B21" t="n">
-        <v>1.33</v>
-      </c>
-      <c r="C21" t="n">
-        <v>5</v>
-      </c>
-      <c r="D21" t="n">
-        <v>8.5</v>
+          <t>UZQ75g6n</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>IZmnZ98g</t>
-        </is>
-      </c>
-      <c r="B22" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="C22" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D22" t="n">
-        <v>3.4</v>
+          <t>6gkNzNqb</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>fJ9e2NvP</t>
-        </is>
-      </c>
-      <c r="B23" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="C23" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="D23" t="n">
-        <v>4.5</v>
+          <t>tAUB4DLh</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>M7fwyWws</t>
-        </is>
-      </c>
-      <c r="B24" t="n">
-        <v>1.38</v>
-      </c>
-      <c r="C24" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="D24" t="n">
-        <v>8</v>
+          <t>pplRZta4</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>vZmXH8wJ</t>
-        </is>
-      </c>
-      <c r="B25" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="C25" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D25" t="n">
-        <v>3</v>
+          <t>v7mVY0EA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>Qy97thGJ</t>
-        </is>
-      </c>
-      <c r="B26" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="C26" t="n">
-        <v>4</v>
-      </c>
-      <c r="D26" t="n">
-        <v>4.2</v>
+          <t>OYJG3Xza</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>4S7BuCVP</t>
-        </is>
-      </c>
-      <c r="B27" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="C27" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D27" t="n">
-        <v>4.5</v>
+          <t>bc9YvOXo</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Y3uxBFrP</t>
-        </is>
-      </c>
-      <c r="B28" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="C28" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="D28" t="n">
-        <v>3.9</v>
+          <t>AReExqFo</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>6LkPJU86</t>
-        </is>
-      </c>
-      <c r="B29" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="C29" t="n">
-        <v>4.75</v>
-      </c>
-      <c r="D29" t="n">
-        <v>5</v>
+          <t>nFu3VR7I</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>0rkTIlOC</t>
-        </is>
-      </c>
-      <c r="B30" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="C30" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D30" t="n">
-        <v>4.33</v>
+          <t>4jjbW7hC</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>zDR36Zjt</t>
-        </is>
-      </c>
-      <c r="B31" t="n">
-        <v>1.48</v>
-      </c>
-      <c r="C31" t="n">
-        <v>5</v>
-      </c>
-      <c r="D31" t="n">
-        <v>5.5</v>
+          <t>dO7WDaxo</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>AgdGLjvf</t>
-        </is>
-      </c>
-      <c r="B32" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="C32" t="n">
-        <v>4.33</v>
-      </c>
-      <c r="D32" t="n">
-        <v>5.25</v>
+          <t>QaifXmw6</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>rLDxzCn4</t>
-        </is>
-      </c>
-      <c r="B33" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="C33" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="D33" t="n">
-        <v>4.35</v>
+          <t>dQnjYTNa</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>lMKTyYHi</t>
-        </is>
-      </c>
-      <c r="B34" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="C34" t="n">
-        <v>3.75</v>
-      </c>
-      <c r="D34" t="n">
-        <v>4.94</v>
+          <t>zBbszjgm</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>1.33</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>8.50</t>
+        </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>UHm3LCXA</t>
-        </is>
-      </c>
-      <c r="B35" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="C35" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="D35" t="n">
-        <v>4.52</v>
+          <t>IZmnZ98g</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>xriBJj2N</t>
-        </is>
-      </c>
-      <c r="B36" t="n">
-        <v>2.68</v>
-      </c>
-      <c r="C36" t="n">
-        <v>3.36</v>
-      </c>
-      <c r="D36" t="n">
-        <v>2.52</v>
+          <t>fJ9e2NvP</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>1.70</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>AVLPxE2o</t>
-        </is>
-      </c>
-      <c r="B37" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="C37" t="n">
-        <v>3.82</v>
-      </c>
-      <c r="D37" t="n">
-        <v>3.51</v>
+          <t>M7fwyWws</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>8.00</t>
+        </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>WpAYzhXc</t>
-        </is>
-      </c>
-      <c r="B38" t="n">
-        <v>2.34</v>
-      </c>
-      <c r="C38" t="n">
-        <v>3.65</v>
-      </c>
-      <c r="D38" t="n">
-        <v>2.71</v>
+          <t>vZmXH8wJ</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>K6tGIAHT</t>
-        </is>
-      </c>
-      <c r="B39" t="n">
-        <v>3.02</v>
-      </c>
-      <c r="C39" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="D39" t="n">
-        <v>2.29</v>
+          <t>Qy97thGJ</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>MFSsEUPp</t>
-        </is>
-      </c>
-      <c r="B40" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="C40" t="n">
-        <v>3.44</v>
-      </c>
-      <c r="D40" t="n">
-        <v>3.44</v>
+          <t>4S7BuCVP</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>Ovm7KWnH</t>
-        </is>
-      </c>
-      <c r="B41" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="C41" t="n">
-        <v>3.29</v>
-      </c>
-      <c r="D41" t="n">
-        <v>2.21</v>
+          <t>Y3uxBFrP</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>jRlaMhI4</t>
-        </is>
-      </c>
-      <c r="B42" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="C42" t="n">
-        <v>3.59</v>
-      </c>
-      <c r="D42" t="n">
-        <v>3.29</v>
+          <t>6LkPJU86</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>O4I2NY2b</t>
-        </is>
-      </c>
-      <c r="B43" t="n">
-        <v>2.63</v>
-      </c>
-      <c r="C43" t="n">
-        <v>3.41</v>
-      </c>
-      <c r="D43" t="n">
-        <v>2.53</v>
+          <t>0rkTIlOC</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>pEJbOEmh</t>
-        </is>
-      </c>
-      <c r="B44" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="C44" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D44" t="n">
-        <v>3.1</v>
+          <t>zDR36Zjt</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>xlGjQzJu</t>
-        </is>
-      </c>
-      <c r="B45" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="C45" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="D45" t="n">
-        <v>3.7</v>
+          <t>AgdGLjvf</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>Us7RP67a</t>
-        </is>
-      </c>
-      <c r="B46" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="C46" t="n">
-        <v>4.35</v>
-      </c>
-      <c r="D46" t="n">
-        <v>6.25</v>
+          <t>rqdPQ79j</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>3.15</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>1.90</t>
+        </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>2XbvN4iI</t>
-        </is>
-      </c>
-      <c r="B47" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="C47" t="n">
-        <v>3</v>
-      </c>
-      <c r="D47" t="n">
-        <v>2.1</v>
+          <t>C05gWToT</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>2.00</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>Ac2nLrMU</t>
-        </is>
-      </c>
-      <c r="B48" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="C48" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D48" t="n">
-        <v>1.8</v>
+          <t>Y96kX9WM</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>5.25</t>
+        </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>W63rMO6O</t>
-        </is>
-      </c>
-      <c r="B49" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="C49" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D49" t="n">
-        <v>5</v>
+          <t>GYBpYkHG</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>zL7NQnhg</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="C50" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="D50" t="n">
-        <v>2.15</v>
+          <t>UuhLRmfp</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>Ot0zOpxC</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>1.65</v>
-      </c>
-      <c r="C51" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D51" t="n">
-        <v>4.5</v>
+          <t>xrDtZV1A</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>tIAVOQM5</t>
-        </is>
-      </c>
-      <c r="B52" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="C52" t="n">
-        <v>4.5</v>
-      </c>
-      <c r="D52" t="n">
-        <v>5.5</v>
+          <t>rLDxzCn4</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>dU8JRSxm</t>
-        </is>
-      </c>
-      <c r="B53" t="n">
-        <v>1.75</v>
-      </c>
-      <c r="C53" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D53" t="n">
-        <v>4.25</v>
+          <t>lMKTyYHi</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>4.94</t>
+        </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>jiKfPfYo</t>
-        </is>
-      </c>
-      <c r="B54" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="C54" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="D54" t="n">
-        <v>3.8</v>
+          <t>UHm3LCXA</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>4.52</t>
+        </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>vgEES8Nt</t>
-        </is>
-      </c>
-      <c r="B55" t="n">
-        <v>1.57</v>
-      </c>
-      <c r="C55" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="D55" t="n">
-        <v>5</v>
+          <t>xriBJj2N</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>2.68</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>2.52</t>
+        </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>2TjopygE</t>
-        </is>
-      </c>
-      <c r="B56" t="n">
-        <v>2.57</v>
-      </c>
-      <c r="C56" t="n">
-        <v>3.74</v>
-      </c>
-      <c r="D56" t="n">
-        <v>2.42</v>
+          <t>AVLPxE2o</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>1.91</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>3.82</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>3.51</t>
+        </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>M9ZFUegR</t>
-        </is>
-      </c>
-      <c r="B57" t="n">
-        <v>3.03</v>
-      </c>
-      <c r="C57" t="n">
-        <v>3.54</v>
-      </c>
-      <c r="D57" t="n">
-        <v>2.19</v>
+          <t>WpAYzhXc</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>2.71</t>
+        </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>E7AjOgWf</t>
-        </is>
-      </c>
-      <c r="B58" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="C58" t="n">
-        <v>3.22</v>
-      </c>
-      <c r="D58" t="n">
-        <v>3.21</v>
+          <t>K6tGIAHT</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>3.02</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>zNbaMX07</t>
-        </is>
-      </c>
-      <c r="B59" t="n">
-        <v>2.29</v>
-      </c>
-      <c r="C59" t="n">
-        <v>3.33</v>
-      </c>
-      <c r="D59" t="n">
-        <v>3.02</v>
+          <t>MFSsEUPp</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>3.44</t>
+        </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>zgX3Xc98</t>
-        </is>
-      </c>
-      <c r="B60" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="C60" t="n">
-        <v>3.55</v>
-      </c>
-      <c r="D60" t="n">
-        <v>4.7</v>
+          <t>Ovm7KWnH</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>3.29</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>2.21</t>
+        </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>EqW7WHOE</t>
-        </is>
-      </c>
-      <c r="B61" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="C61" t="n">
-        <v>3.43</v>
-      </c>
-      <c r="D61" t="n">
-        <v>2.65</v>
+          <t>jRlaMhI4</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>2.06</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>3.59</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>3.29</t>
+        </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>lQ23LiGD</t>
-        </is>
-      </c>
-      <c r="B62" t="n">
-        <v>2.17</v>
-      </c>
-      <c r="C62" t="n">
-        <v>3.51</v>
-      </c>
-      <c r="D62" t="n">
-        <v>3.1</v>
+          <t>O4I2NY2b</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>3.41</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>86VBVyvL</t>
-        </is>
-      </c>
-      <c r="B63" t="n">
-        <v>2.83</v>
-      </c>
-      <c r="C63" t="n">
-        <v>3.56</v>
-      </c>
-      <c r="D63" t="n">
-        <v>2.3</v>
+          <t>pEJbOEmh</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>SjCrQF1r</t>
-        </is>
-      </c>
-      <c r="B64" t="n">
-        <v>1.82</v>
-      </c>
-      <c r="C64" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="D64" t="n">
-        <v>3.64</v>
+          <t>xlGjQzJu</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>6sBnPZGl</t>
-        </is>
-      </c>
-      <c r="B65" t="n">
-        <v>7.85</v>
-      </c>
-      <c r="C65" t="n">
-        <v>4.67</v>
-      </c>
-      <c r="D65" t="n">
-        <v>1.38</v>
+          <t>Us7RP67a</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>hb9fNDo1</t>
-        </is>
-      </c>
-      <c r="B66" t="n">
-        <v>2.04</v>
-      </c>
-      <c r="C66" t="n">
-        <v>3.45</v>
-      </c>
-      <c r="D66" t="n">
-        <v>3.45</v>
+          <t>2XbvN4iI</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>tflZ7nSp</t>
+          <t>Ac2nLrMU</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>1.80</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>raSHWV4o</t>
+          <t>W63rMO6O</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>zg5jGAK4</t>
+          <t>zL7NQnhg</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.15</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>ld9fFUZA</t>
+          <t>Ot0zOpxC</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>WKbaElkH</t>
+          <t>tIAVOQM5</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.45</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>ABc3D84N</t>
+          <t>dU8JRSxm</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.25</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>vo27CSJT</t>
+          <t>jiKfPfYo</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.80</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>MTkoJCzn</t>
+          <t>vgEES8Nt</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>hK8xvrmh</t>
+          <t>2TjopygE</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.74</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>2.42</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>rwisKhLu</t>
+          <t>M9ZFUegR</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.19</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>2u7rIWkh</t>
+          <t>E7AjOgWf</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.24</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.21</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>tW5nHj5b</t>
+          <t>zNbaMX07</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>3.02</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>WA7tw22b</t>
+          <t>zgX3Xc98</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>4.70</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>C05gWToT</t>
+          <t>EqW7WHOE</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>2.65</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>Y96kX9WM</t>
+          <t>lQ23LiGD</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>GYBpYkHG</t>
+          <t>86VBVyvL</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.56</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>2.30</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>UuhLRmfp</t>
+          <t>SjCrQF1r</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>3.64</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>xrDtZV1A</t>
+          <t>6sBnPZGl</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>7.85</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>1.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="1" t="inlineStr">
+        <is>
+          <t>hb9fNDo1</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>3.45</t>
         </is>
       </c>
     </row>

--- a/p6_deployment/data/usa/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/p6_deployment/data/usa/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D85"/>
+  <dimension ref="A1:D108"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -448,166 +448,166 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>tflZ7nSp</t>
+          <t>UT5bq9li</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.30</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>7.50</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>raSHWV4o</t>
+          <t>Ma0gz0nH</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>zg5jGAK4</t>
+          <t>8K42rT3c</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>5.75</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>ld9fFUZA</t>
+          <t>Sx1kytXA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>7.50</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>WKbaElkH</t>
+          <t>2NHGKPBj</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>ABc3D84N</t>
+          <t>4nxtRRYM</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>vo27CSJT</t>
+          <t>IktpQolT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2.80</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>MTkoJCzn</t>
+          <t>OWICL5dp</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -617,217 +617,217 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.50</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>hK8xvrmh</t>
+          <t>z7pPU9Zc</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>5.25</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>8.00</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>rwisKhLu</t>
+          <t>EcqTTTl4</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>2u7rIWkh</t>
+          <t>tpoLVkKi</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>tW5nHj5b</t>
+          <t>ln2oxMH4</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>WA7tw22b</t>
+          <t>WYwYSm4A</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>AkMS0VKH</t>
+          <t>APxxS7JG</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>2.80</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>hEBXakzO</t>
+          <t>tflZ7nSp</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>3.50</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>6HFya9kU</t>
+          <t>raSHWV4o</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>WbNO1B5B</t>
+          <t>zg5jGAK4</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.80</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>2.05</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>2PIK2ij5</t>
+          <t>ld9fFUZA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -837,41 +837,41 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>2.90</t>
+          <t>4.00</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>lIfIy3Ui</t>
+          <t>WKbaElkH</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
           <t>3.90</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>UZQ75g6n</t>
+          <t>ABc3D84N</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -881,261 +881,261 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>6gkNzNqb</t>
+          <t>vo27CSJT</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.50</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>tAUB4DLh</t>
+          <t>MTkoJCzn</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.75</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>pplRZta4</t>
+          <t>hK8xvrmh</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>3.00</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>2.25</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>v7mVY0EA</t>
+          <t>rwisKhLu</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>3.40</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>OYJG3Xza</t>
+          <t>2u7rIWkh</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.70</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>bc9YvOXo</t>
+          <t>tW5nHj5b</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>3.25</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>2.05</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>AReExqFo</t>
+          <t>WA7tw22b</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>3.80</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>nFu3VR7I</t>
+          <t>AkMS0VKH</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>4jjbW7hC</t>
+          <t>hEBXakzO</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>2.45</t>
+          <t>2.60</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.55</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>dO7WDaxo</t>
+          <t>6HFya9kU</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>1.50</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>6.00</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>QaifXmw6</t>
+          <t>WbNO1B5B</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>2.60</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>dQnjYTNa</t>
+          <t>2PIK2ij5</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -1145,107 +1145,107 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>2.90</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>zBbszjgm</t>
+          <t>lIfIy3Ui</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.50</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>IZmnZ98g</t>
+          <t>UZQ75g6n</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>fJ9e2NvP</t>
+          <t>6gkNzNqb</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.20</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.90</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>M7fwyWws</t>
+          <t>tAUB4DLh</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.00</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>vZmXH8wJ</t>
+          <t>pplRZta4</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>2.25</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -1255,239 +1255,239 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>4.10</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>Qy97thGJ</t>
+          <t>v7mVY0EA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.63</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>4.00</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>4.20</t>
+          <t>2.60</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>4S7BuCVP</t>
+          <t>OYJG3Xza</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.60</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>Y3uxBFrP</t>
+          <t>bc9YvOXo</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.80</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>6LkPJU86</t>
+          <t>AReExqFo</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>0rkTIlOC</t>
+          <t>nFu3VR7I</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>3.10</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>zDR36Zjt</t>
+          <t>4jjbW7hC</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>2.45</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>2.80</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>AgdGLjvf</t>
+          <t>dO7WDaxo</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4.33</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>rqdPQ79j</t>
+          <t>QaifXmw6</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>3.15</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>1.90</t>
+          <t>2.60</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>C05gWToT</t>
+          <t>dQnjYTNa</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>3.40</t>
+          <t>3.60</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>Y96kX9WM</t>
+          <t>zBbszjgm</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>1.52</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>5.25</t>
+          <t>8.50</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>GYBpYkHG</t>
+          <t>IZmnZ98g</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>1.75</t>
+          <t>2.10</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -1497,498 +1497,498 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>3.40</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>UuhLRmfp</t>
+          <t>fJ9e2NvP</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>3.20</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>xrDtZV1A</t>
+          <t>M7fwyWws</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>2.40</t>
+          <t>8.00</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>rLDxzCn4</t>
+          <t>vZmXH8wJ</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.25</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>3.90</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>3.00</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>lMKTyYHi</t>
+          <t>Qy97thGJ</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>3.75</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>4.94</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>UHm3LCXA</t>
+          <t>4S7BuCVP</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.75</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.70</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>4.52</t>
+          <t>4.50</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>xriBJj2N</t>
+          <t>Y3uxBFrP</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>2.68</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>3.36</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>3.90</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>AVLPxE2o</t>
+          <t>6LkPJU86</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>1.91</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>3.82</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>5.00</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>WpAYzhXc</t>
+          <t>0rkTIlOC</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>2.71</t>
+          <t>4.33</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>K6tGIAHT</t>
+          <t>zDR36Zjt</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>1.48</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>5.00</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>5.50</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>MFSsEUPp</t>
+          <t>AgdGLjvf</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.57</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>4.33</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>3.44</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>Ovm7KWnH</t>
+          <t>W4YFmVG3</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>2.21</t>
+          <t>2.75</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>jRlaMhI4</t>
+          <t>KU63vRwj</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>2.06</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>3.59</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>3.29</t>
+          <t>2.55</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>O4I2NY2b</t>
+          <t>0pQWqmGS</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>2.63</t>
+          <t>1.80</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>3.41</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>2.53</t>
+          <t>4.20</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>pEJbOEmh</t>
+          <t>plz8kini</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.45</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>1.95</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>xlGjQzJu</t>
+          <t>AeXJnkW9</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.38</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>6.40</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>Us7RP67a</t>
+          <t>2gCbu7Oq</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>1.42</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>4.35</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>3.05</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>2XbvN4iI</t>
+          <t>OvZBlB1c</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>3.50</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>3.00</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>2.10</t>
+          <t>4.25</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>Ac2nLrMU</t>
+          <t>hKMOo9oG</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.50</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>1.80</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>W63rMO6O</t>
+          <t>6NQSpT0M</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>1.50</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.55</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>2.70</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>zL7NQnhg</t>
+          <t>rqdPQ79j</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>3.70</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>2.15</t>
+          <t>1.90</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>Ot0zOpxC</t>
+          <t>C05gWToT</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>2.00</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>3.40</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>3.25</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>tIAVOQM5</t>
+          <t>Y96kX9WM</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>1.45</t>
+          <t>1.52</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>4.10</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>5.50</t>
+          <t>5.25</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>dU8JRSxm</t>
+          <t>GYBpYkHG</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
@@ -2003,41 +2003,41 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>4.10</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>jiKfPfYo</t>
+          <t>UuhLRmfp</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>3.60</t>
+          <t>3.20</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>3.80</t>
+          <t>2.70</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>vgEES8Nt</t>
+          <t>xrDtZV1A</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>1.57</t>
+          <t>2.50</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -2047,247 +2047,753 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>5.00</t>
+          <t>2.40</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>2TjopygE</t>
+          <t>rLDxzCn4</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>3.74</t>
+          <t>3.90</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>4.35</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>M9ZFUegR</t>
+          <t>lMKTyYHi</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>3.75</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>4.94</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>E7AjOgWf</t>
+          <t>UHm3LCXA</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>3.21</t>
+          <t>4.52</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>zNbaMX07</t>
+          <t>xriBJj2N</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.68</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>3.33</t>
+          <t>3.36</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>3.02</t>
+          <t>2.52</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>zgX3Xc98</t>
+          <t>AVLPxE2o</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.91</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>3.55</t>
+          <t>3.82</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>4.70</t>
+          <t>3.51</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>EqW7WHOE</t>
+          <t>WpAYzhXc</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>2.50</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.71</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>lQ23LiGD</t>
+          <t>K6tGIAHT</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>3.02</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.33</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>3.10</t>
+          <t>2.29</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>86VBVyvL</t>
+          <t>MFSsEUPp</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>3.56</t>
+          <t>3.44</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>2.30</t>
+          <t>3.44</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>SjCrQF1r</t>
+          <t>Ovm7KWnH</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>3.29</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>3.64</t>
+          <t>2.21</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>6sBnPZGl</t>
+          <t>jRlaMhI4</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>7.85</t>
+          <t>2.06</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>3.59</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>1.38</t>
+          <t>3.29</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
+          <t>O4I2NY2b</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>3.41</t>
+        </is>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>2.53</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="1" t="inlineStr">
+        <is>
+          <t>pEJbOEmh</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="1" t="inlineStr">
+        <is>
+          <t>xlGjQzJu</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="1" t="inlineStr">
+        <is>
+          <t>Us7RP67a</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>1.42</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>4.35</t>
+        </is>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>6.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="1" t="inlineStr">
+        <is>
+          <t>2XbvN4iI</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="1" t="inlineStr">
+        <is>
+          <t>Ac2nLrMU</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="1" t="inlineStr">
+        <is>
+          <t>W63rMO6O</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="1" t="inlineStr">
+        <is>
+          <t>zL7NQnhg</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="1" t="inlineStr">
+        <is>
+          <t>Ot0zOpxC</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="1" t="inlineStr">
+        <is>
+          <t>tIAVOQM5</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="1" t="inlineStr">
+        <is>
+          <t>dU8JRSxm</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>4.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="1" t="inlineStr">
+        <is>
+          <t>jiKfPfYo</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="1" t="inlineStr">
+        <is>
+          <t>vgEES8Nt</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="1" t="inlineStr">
+        <is>
+          <t>2TjopygE</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>2.57</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>3.74</t>
+        </is>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>2.42</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="1" t="inlineStr">
+        <is>
+          <t>M9ZFUegR</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>3.03</t>
+        </is>
+      </c>
+      <c r="C99" t="inlineStr">
+        <is>
+          <t>3.54</t>
+        </is>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>2.19</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="1" t="inlineStr">
+        <is>
+          <t>E7AjOgWf</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>2.24</t>
+        </is>
+      </c>
+      <c r="C100" t="inlineStr">
+        <is>
+          <t>3.22</t>
+        </is>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>3.21</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="1" t="inlineStr">
+        <is>
+          <t>zNbaMX07</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
+      <c r="C101" t="inlineStr">
+        <is>
+          <t>3.33</t>
+        </is>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>3.02</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="1" t="inlineStr">
+        <is>
+          <t>zgX3Xc98</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>1.74</t>
+        </is>
+      </c>
+      <c r="C102" t="inlineStr">
+        <is>
+          <t>3.55</t>
+        </is>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>4.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="1" t="inlineStr">
+        <is>
+          <t>EqW7WHOE</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+      <c r="C103" t="inlineStr">
+        <is>
+          <t>3.43</t>
+        </is>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>2.65</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="1" t="inlineStr">
+        <is>
+          <t>lQ23LiGD</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="C104" t="inlineStr">
+        <is>
+          <t>3.51</t>
+        </is>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="1" t="inlineStr">
+        <is>
+          <t>86VBVyvL</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="C105" t="inlineStr">
+        <is>
+          <t>3.56</t>
+        </is>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="1" t="inlineStr">
+        <is>
+          <t>SjCrQF1r</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="C106" t="inlineStr">
+        <is>
+          <t>4.06</t>
+        </is>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>3.64</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="1" t="inlineStr">
+        <is>
+          <t>6sBnPZGl</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>7.85</t>
+        </is>
+      </c>
+      <c r="C107" t="inlineStr">
+        <is>
+          <t>4.67</t>
+        </is>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>1.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="1" t="inlineStr">
+        <is>
           <t>hb9fNDo1</t>
         </is>
       </c>
-      <c r="B85" t="inlineStr">
+      <c r="B108" t="inlineStr">
         <is>
           <t>2.04</t>
         </is>
       </c>
-      <c r="C85" t="inlineStr">
+      <c r="C108" t="inlineStr">
         <is>
           <t>3.45</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr">
+      <c r="D108" t="inlineStr">
         <is>
           <t>3.45</t>
         </is>

--- a/p6_deployment/data/usa/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/p6_deployment/data/usa/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D110"/>
+  <dimension ref="A1:D134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2177,6 +2177,534 @@
       <c r="C110" t="inlineStr"/>
       <c r="D110" t="inlineStr"/>
     </row>
+    <row r="111">
+      <c r="A111" s="1" t="inlineStr">
+        <is>
+          <t>xbHaKGH7</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>1.48</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>5.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" s="1" t="inlineStr">
+        <is>
+          <t>v3erq0f8</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" s="1" t="inlineStr">
+        <is>
+          <t>IgfnrK9E</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>2.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" s="1" t="inlineStr">
+        <is>
+          <t>nTbjsvPK</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>5.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" s="1" t="inlineStr">
+        <is>
+          <t>YyTMIXGq</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1.65</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" s="1" t="inlineStr">
+        <is>
+          <t>zZKrObIr</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="1" t="inlineStr">
+        <is>
+          <t>hAFmNIXl</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="1" t="inlineStr">
+        <is>
+          <t>QNDeLd21</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>3.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="1" t="inlineStr">
+        <is>
+          <t>W0EiMxme</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="1" t="inlineStr">
+        <is>
+          <t>G0IRHiWk</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>1.73</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="1" t="inlineStr">
+        <is>
+          <t>fiHVGBod</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>2.45</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>2.63</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="1" t="inlineStr">
+        <is>
+          <t>4nbBt7Y9</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="1" t="inlineStr">
+        <is>
+          <t>b9cFuRmG</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="1" t="inlineStr">
+        <is>
+          <t>jqf7smJ3</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>1.75</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="1" t="inlineStr">
+        <is>
+          <t>63KkwxaD</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>1.47</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>4.40</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>5.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="1" t="inlineStr">
+        <is>
+          <t>xOSYtKal</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>2.60</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>3.35</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>2.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="1" t="inlineStr">
+        <is>
+          <t>SCLovIq7</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>2.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="1" t="inlineStr">
+        <is>
+          <t>bXTUs0pr</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>4.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="1" t="inlineStr">
+        <is>
+          <t>6eQQ1LyE</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>3.45</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="1" t="inlineStr">
+        <is>
+          <t>WO01aSFF</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>2.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="1" t="inlineStr">
+        <is>
+          <t>KnIwtvFf</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>3.65</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="1" t="inlineStr">
+        <is>
+          <t>YkMsubU0</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>4.10</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="1" t="inlineStr">
+        <is>
+          <t>hY1c0809</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>1.87</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="1" t="inlineStr">
+        <is>
+          <t>A9Ch1lo3</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>1.66</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>3.60</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>4.15</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/usa/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/p6_deployment/data/usa/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D134"/>
+  <dimension ref="A1:D178"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2183,20 +2183,14 @@
           <t>xbHaKGH7</t>
         </is>
       </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>1.48</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="D111" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
+      <c r="B111" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="C111" t="n">
+        <v>5</v>
+      </c>
+      <c r="D111" t="n">
+        <v>5.5</v>
       </c>
     </row>
     <row r="112">
@@ -2205,20 +2199,14 @@
           <t>v3erq0f8</t>
         </is>
       </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D112" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
+      <c r="B112" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="C112" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D112" t="n">
+        <v>4.1</v>
       </c>
     </row>
     <row r="113">
@@ -2227,20 +2215,14 @@
           <t>IgfnrK9E</t>
         </is>
       </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D113" t="inlineStr">
-        <is>
-          <t>2.30</t>
-        </is>
+      <c r="B113" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="C113" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D113" t="n">
+        <v>2.3</v>
       </c>
     </row>
     <row r="114">
@@ -2249,20 +2231,14 @@
           <t>nTbjsvPK</t>
         </is>
       </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D114" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="B114" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C114" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D114" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="115">
@@ -2271,20 +2247,14 @@
           <t>YyTMIXGq</t>
         </is>
       </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>1.65</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="D115" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
+      <c r="B115" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C115" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D115" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="116">
@@ -2293,20 +2263,14 @@
           <t>zZKrObIr</t>
         </is>
       </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>2.80</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D116" t="inlineStr">
-        <is>
-          <t>2.38</t>
-        </is>
+      <c r="B116" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C116" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D116" t="n">
+        <v>2.38</v>
       </c>
     </row>
     <row r="117">
@@ -2315,20 +2279,14 @@
           <t>hAFmNIXl</t>
         </is>
       </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>1.83</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D117" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
+      <c r="B117" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="C117" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D117" t="n">
+        <v>4.33</v>
       </c>
     </row>
     <row r="118">
@@ -2337,20 +2295,14 @@
           <t>QNDeLd21</t>
         </is>
       </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D118" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="B118" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C118" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D118" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="119">
@@ -2359,20 +2311,14 @@
           <t>W0EiMxme</t>
         </is>
       </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="D119" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
+      <c r="B119" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C119" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D119" t="n">
+        <v>3.7</v>
       </c>
     </row>
     <row r="120">
@@ -2381,20 +2327,14 @@
           <t>G0IRHiWk</t>
         </is>
       </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>1.73</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D120" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
+      <c r="B120" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="C120" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D120" t="n">
+        <v>4.2</v>
       </c>
     </row>
     <row r="121">
@@ -2403,20 +2343,14 @@
           <t>fiHVGBod</t>
         </is>
       </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>2.45</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D121" t="inlineStr">
-        <is>
-          <t>2.63</t>
-        </is>
+      <c r="B121" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="C121" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D121" t="n">
+        <v>2.63</v>
       </c>
     </row>
     <row r="122">
@@ -2425,20 +2359,14 @@
           <t>4nbBt7Y9</t>
         </is>
       </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D122" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
+      <c r="B122" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="C122" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D122" t="n">
+        <v>2.1</v>
       </c>
     </row>
     <row r="123">
@@ -2447,20 +2375,14 @@
           <t>b9cFuRmG</t>
         </is>
       </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>1.67</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D123" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
+      <c r="B123" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="C123" t="n">
+        <v>4</v>
+      </c>
+      <c r="D123" t="n">
+        <v>4.75</v>
       </c>
     </row>
     <row r="124">
@@ -2469,20 +2391,14 @@
           <t>jqf7smJ3</t>
         </is>
       </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>1.75</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D124" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
+      <c r="B124" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="C124" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D124" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="125">
@@ -2491,20 +2407,14 @@
           <t>63KkwxaD</t>
         </is>
       </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>1.47</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>4.40</t>
-        </is>
-      </c>
-      <c r="D125" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
+      <c r="B125" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="C125" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D125" t="n">
+        <v>5.75</v>
       </c>
     </row>
     <row r="126">
@@ -2513,20 +2423,14 @@
           <t>xOSYtKal</t>
         </is>
       </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>2.60</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>3.35</t>
-        </is>
-      </c>
-      <c r="D126" t="inlineStr">
-        <is>
-          <t>2.50</t>
-        </is>
+      <c r="B126" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C126" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="D126" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="127">
@@ -2535,20 +2439,14 @@
           <t>SCLovIq7</t>
         </is>
       </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>3.50</t>
-        </is>
-      </c>
-      <c r="D127" t="inlineStr">
-        <is>
-          <t>2.70</t>
-        </is>
+      <c r="B127" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C127" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D127" t="n">
+        <v>2.7</v>
       </c>
     </row>
     <row r="128">
@@ -2557,20 +2455,14 @@
           <t>bXTUs0pr</t>
         </is>
       </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D128" t="inlineStr">
-        <is>
-          <t>4.85</t>
-        </is>
+      <c r="B128" t="n">
+        <v>1.52</v>
+      </c>
+      <c r="C128" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D128" t="n">
+        <v>4.85</v>
       </c>
     </row>
     <row r="129">
@@ -2579,20 +2471,14 @@
           <t>6eQQ1LyE</t>
         </is>
       </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>2.08</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>3.45</t>
-        </is>
-      </c>
-      <c r="D129" t="inlineStr">
-        <is>
-          <t>3.10</t>
-        </is>
+      <c r="B129" t="n">
+        <v>2.08</v>
+      </c>
+      <c r="C129" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="D129" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="130">
@@ -2601,20 +2487,14 @@
           <t>WO01aSFF</t>
         </is>
       </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>2.90</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
-      </c>
-      <c r="D130" t="inlineStr">
-        <is>
-          <t>2.25</t>
-        </is>
+      <c r="B130" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C130" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D130" t="n">
+        <v>2.25</v>
       </c>
     </row>
     <row r="131">
@@ -2623,20 +2503,14 @@
           <t>KnIwtvFf</t>
         </is>
       </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>3.65</t>
-        </is>
-      </c>
-      <c r="D131" t="inlineStr">
-        <is>
-          <t>1.85</t>
-        </is>
+      <c r="B131" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="C131" t="n">
+        <v>3.65</v>
+      </c>
+      <c r="D131" t="n">
+        <v>1.85</v>
       </c>
     </row>
     <row r="132">
@@ -2645,20 +2519,14 @@
           <t>YkMsubU0</t>
         </is>
       </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D132" t="inlineStr">
-        <is>
-          <t>1.78</t>
-        </is>
+      <c r="B132" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="C132" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D132" t="n">
+        <v>1.78</v>
       </c>
     </row>
     <row r="133">
@@ -2667,20 +2535,14 @@
           <t>hY1c0809</t>
         </is>
       </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>1.87</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D133" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
+      <c r="B133" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="C133" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D133" t="n">
+        <v>3.7</v>
       </c>
     </row>
     <row r="134">
@@ -2689,19 +2551,753 @@
           <t>A9Ch1lo3</t>
         </is>
       </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>1.66</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
+      <c r="B134" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="C134" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D134" t="n">
+        <v>4.15</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="1" t="inlineStr">
+        <is>
+          <t>OU7ZWg1D</t>
+        </is>
+      </c>
+      <c r="B135" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C135" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D135" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="1" t="inlineStr">
+        <is>
+          <t>IHxZYFW0</t>
+        </is>
+      </c>
+      <c r="B136" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C136" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D136" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="1" t="inlineStr">
+        <is>
+          <t>UN8LwZh9</t>
+        </is>
+      </c>
+      <c r="B137" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="C137" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D137" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="1" t="inlineStr">
+        <is>
+          <t>pv9VXZo7</t>
+        </is>
+      </c>
+      <c r="B138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C138" t="n">
+        <v>4</v>
+      </c>
+      <c r="D138" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="1" t="inlineStr">
+        <is>
+          <t>vRwVZeHf</t>
+        </is>
+      </c>
+      <c r="B139" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C139" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D139" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="1" t="inlineStr">
+        <is>
+          <t>QJcftbvR</t>
+        </is>
+      </c>
+      <c r="B140" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C140" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D140" t="n">
+        <v>3.5</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="1" t="inlineStr">
+        <is>
+          <t>p4vRzx2l</t>
+        </is>
+      </c>
+      <c r="B141" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C141" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="D141" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="1" t="inlineStr">
+        <is>
+          <t>88KCueOd</t>
+        </is>
+      </c>
+      <c r="B142" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="C142" t="n">
+        <v>5</v>
+      </c>
+      <c r="D142" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="1" t="inlineStr">
+        <is>
+          <t>naJGvFw3</t>
+        </is>
+      </c>
+      <c r="B143" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="C143" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D143" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="1" t="inlineStr">
+        <is>
+          <t>W0zNyInr</t>
+        </is>
+      </c>
+      <c r="B144" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="C144" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D144" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="1" t="inlineStr">
+        <is>
+          <t>GUF0eJEs</t>
+        </is>
+      </c>
+      <c r="B145" t="n">
+        <v>1.72</v>
+      </c>
+      <c r="C145" t="n">
+        <v>3.91</v>
+      </c>
+      <c r="D145" t="n">
+        <v>4.3</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="1" t="inlineStr">
+        <is>
+          <t>v9OYaa6Q</t>
+        </is>
+      </c>
+      <c r="B146" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="C146" t="n">
+        <v>4.15</v>
+      </c>
+      <c r="D146" t="n">
+        <v>4.66</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="1" t="inlineStr">
+        <is>
+          <t>pnPU0uiK</t>
+        </is>
+      </c>
+      <c r="B147" t="n">
+        <v>1.96</v>
+      </c>
+      <c r="C147" t="n">
+        <v>3.72</v>
+      </c>
+      <c r="D147" t="n">
+        <v>3.34</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="1" t="inlineStr">
+        <is>
+          <t>YakQgH8Q</t>
+        </is>
+      </c>
+      <c r="B148" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="C148" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D148" t="n">
+        <v>2.15</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="1" t="inlineStr">
+        <is>
+          <t>jy0LfcgK</t>
+        </is>
+      </c>
+      <c r="B149" t="n">
+        <v>1.53</v>
+      </c>
+      <c r="C149" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D149" t="n">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="1" t="inlineStr">
+        <is>
+          <t>xYeHewvE</t>
+        </is>
+      </c>
+      <c r="B150" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C150" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D150" t="n">
+        <v>2.63</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="1" t="inlineStr">
+        <is>
+          <t>bg55fwUm</t>
+        </is>
+      </c>
+      <c r="B151" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C151" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D151" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="1" t="inlineStr">
+        <is>
+          <t>xp49gcqf</t>
+        </is>
+      </c>
+      <c r="B152" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C152" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="D152" t="n">
+        <v>3.15</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="1" t="inlineStr">
+        <is>
+          <t>6J8DhHb0</t>
+        </is>
+      </c>
+      <c r="B153" t="n">
+        <v>1.68</v>
+      </c>
+      <c r="C153" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="D153" t="n">
+        <v>4.25</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="1" t="inlineStr">
+        <is>
+          <t>WfXCpDVC</t>
+        </is>
+      </c>
+      <c r="B154" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="C154" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D154" t="n">
+        <v>6.5</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" s="1" t="inlineStr">
+        <is>
+          <t>QcU4nZ00</t>
+        </is>
+      </c>
+      <c r="B155" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="C155" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D155" t="n">
+        <v>2.4</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="1" t="inlineStr">
+        <is>
+          <t>xYX8ogG6</t>
+        </is>
+      </c>
+      <c r="B156" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="C156" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D156" t="n">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="1" t="inlineStr">
+        <is>
+          <t>xlCTyDNL</t>
+        </is>
+      </c>
+      <c r="B157" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="C157" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D157" t="n">
+        <v>2.55</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="1" t="inlineStr">
+        <is>
+          <t>rRCPxg8F</t>
+        </is>
+      </c>
+      <c r="B158" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="C158" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="D158" t="n">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="1" t="inlineStr">
+        <is>
+          <t>z9yhkyHs</t>
+        </is>
+      </c>
+      <c r="B159" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C159" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D159" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="1" t="inlineStr">
+        <is>
+          <t>4rtdleWm</t>
+        </is>
+      </c>
+      <c r="B160" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="C160" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D160" t="n">
+        <v>4.75</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" s="1" t="inlineStr">
+        <is>
+          <t>rZv0mFof</t>
+        </is>
+      </c>
+      <c r="B161" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="C161" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D161" t="n">
+        <v>2.35</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" s="1" t="inlineStr">
+        <is>
+          <t>hCl8EbLJ</t>
+        </is>
+      </c>
+      <c r="B162" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="C162" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D162" t="n">
+        <v>2.05</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" s="1" t="inlineStr">
+        <is>
+          <t>W2mCDIzQ</t>
+        </is>
+      </c>
+      <c r="B163" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="C163" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D163" t="n">
+        <v>1.9</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" s="1" t="inlineStr">
+        <is>
+          <t>jmUr8dbm</t>
+        </is>
+      </c>
+      <c r="B164" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="C164" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="D164" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" s="1" t="inlineStr">
+        <is>
+          <t>v90QkFrJ</t>
+        </is>
+      </c>
+      <c r="B165" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="C165" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D165" t="n">
+        <v>7.5</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" s="1" t="inlineStr">
+        <is>
+          <t>pA7HiyE6</t>
+        </is>
+      </c>
+      <c r="B166" t="n">
+        <v>2.85</v>
+      </c>
+      <c r="C166" t="n">
+        <v>3.25</v>
+      </c>
+      <c r="D166" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" s="1" t="inlineStr">
+        <is>
+          <t>CdVv9xqs</t>
+        </is>
+      </c>
+      <c r="B167" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="C167" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D167" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" s="1" t="inlineStr">
+        <is>
+          <t>dx5Z1E0m</t>
+        </is>
+      </c>
+      <c r="B168" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="C168" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="D168" t="n">
+        <v>5.5</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" s="1" t="inlineStr">
+        <is>
+          <t>v1fv1YFg</t>
+        </is>
+      </c>
+      <c r="B169" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C169" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="D169" t="n">
+        <v>4.33</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" s="1" t="inlineStr">
+        <is>
+          <t>rZ0V2fos</t>
+        </is>
+      </c>
+      <c r="B170" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C170" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D170" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" s="1" t="inlineStr">
+        <is>
+          <t>QgE37zwQ</t>
+        </is>
+      </c>
+      <c r="B171" t="n">
+        <v>2.35</v>
+      </c>
+      <c r="C171" t="n">
+        <v>4</v>
+      </c>
+      <c r="D171" t="n">
+        <v>2.63</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" s="1" t="inlineStr">
+        <is>
+          <t>n3Fa8GNJ</t>
+        </is>
+      </c>
+      <c r="B172" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C172" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D172" t="n">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" s="1" t="inlineStr">
+        <is>
+          <t>0YXnLoFb</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>1.17</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>7.00</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>12.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" s="1" t="inlineStr">
+        <is>
+          <t>d0ReJPqB</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>2.88</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" s="1" t="inlineStr">
+        <is>
+          <t>APpAklQ6</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>2.80</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" s="1" t="inlineStr">
+        <is>
+          <t>SKZvN7pn</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>3.70</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" s="1" t="inlineStr">
+        <is>
+          <t>pATn7GDg</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>2.40</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
         <is>
           <t>3.60</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr">
-        <is>
-          <t>4.15</t>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>2.55</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" s="1" t="inlineStr">
+        <is>
+          <t>bDXj6zTa</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>4.50</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>1.65</t>
         </is>
       </c>
     </row>

--- a/p6_deployment/data/usa/missing/data_understanding/all/df_match_odds_miss.xlsx
+++ b/p6_deployment/data/usa/missing/data_understanding/all/df_match_odds_miss.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D215"/>
+  <dimension ref="A1:D238"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3635,20 +3635,14 @@
           <t>08pcD25G</t>
         </is>
       </c>
-      <c r="B201" t="inlineStr">
-        <is>
-          <t>1.44</t>
-        </is>
-      </c>
-      <c r="C201" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
-      </c>
-      <c r="D201" t="inlineStr">
-        <is>
-          <t>6.00</t>
-        </is>
+      <c r="B201" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="C201" t="n">
+        <v>5</v>
+      </c>
+      <c r="D201" t="n">
+        <v>6</v>
       </c>
     </row>
     <row r="202">
@@ -3657,20 +3651,14 @@
           <t>KdTaErjA</t>
         </is>
       </c>
-      <c r="B202" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="C202" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D202" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
+      <c r="B202" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C202" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D202" t="n">
+        <v>3.6</v>
       </c>
     </row>
     <row r="203">
@@ -3679,20 +3667,14 @@
           <t>vaq1CMKM</t>
         </is>
       </c>
-      <c r="B203" t="inlineStr">
-        <is>
-          <t>3.00</t>
-        </is>
-      </c>
-      <c r="C203" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D203" t="inlineStr">
-        <is>
-          <t>2.15</t>
-        </is>
+      <c r="B203" t="n">
+        <v>3</v>
+      </c>
+      <c r="C203" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D203" t="n">
+        <v>2.15</v>
       </c>
     </row>
     <row r="204">
@@ -3701,20 +3683,14 @@
           <t>YLr5BtzT</t>
         </is>
       </c>
-      <c r="B204" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="C204" t="inlineStr">
-        <is>
-          <t>4.20</t>
-        </is>
-      </c>
-      <c r="D204" t="inlineStr">
-        <is>
-          <t>5.00</t>
-        </is>
+      <c r="B204" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="C204" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="D204" t="n">
+        <v>5</v>
       </c>
     </row>
     <row r="205">
@@ -3723,20 +3699,14 @@
           <t>rRYfhY72</t>
         </is>
       </c>
-      <c r="B205" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="C205" t="inlineStr">
-        <is>
-          <t>4.33</t>
-        </is>
-      </c>
-      <c r="D205" t="inlineStr">
-        <is>
-          <t>5.25</t>
-        </is>
+      <c r="B205" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C205" t="n">
+        <v>4.33</v>
+      </c>
+      <c r="D205" t="n">
+        <v>5.25</v>
       </c>
     </row>
     <row r="206">
@@ -3745,20 +3715,14 @@
           <t>YuRmHp6i</t>
         </is>
       </c>
-      <c r="B206" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="C206" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D206" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
+      <c r="B206" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C206" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D206" t="n">
+        <v>3.9</v>
       </c>
     </row>
     <row r="207">
@@ -3767,20 +3731,14 @@
           <t>nqViG4Lc</t>
         </is>
       </c>
-      <c r="B207" t="inlineStr">
-        <is>
-          <t>1.95</t>
-        </is>
-      </c>
-      <c r="C207" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="D207" t="inlineStr">
-        <is>
-          <t>3.40</t>
-        </is>
+      <c r="B207" t="n">
+        <v>1.95</v>
+      </c>
+      <c r="C207" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D207" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="208">
@@ -3789,20 +3747,14 @@
           <t>t6UeFOz4</t>
         </is>
       </c>
-      <c r="B208" t="inlineStr">
-        <is>
-          <t>2.88</t>
-        </is>
-      </c>
-      <c r="C208" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
-      </c>
-      <c r="D208" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
+      <c r="B208" t="n">
+        <v>2.88</v>
+      </c>
+      <c r="C208" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D208" t="n">
+        <v>2.35</v>
       </c>
     </row>
     <row r="209">
@@ -3811,20 +3763,14 @@
           <t>noMTBkUB</t>
         </is>
       </c>
-      <c r="B209" t="inlineStr">
-        <is>
-          <t>2.10</t>
-        </is>
-      </c>
-      <c r="C209" t="inlineStr">
-        <is>
-          <t>3.75</t>
-        </is>
-      </c>
-      <c r="D209" t="inlineStr">
-        <is>
-          <t>3.20</t>
-        </is>
+      <c r="B209" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C209" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="D209" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="210">
@@ -3833,20 +3779,14 @@
           <t>hpl1gsEp</t>
         </is>
       </c>
-      <c r="B210" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="C210" t="inlineStr">
-        <is>
-          <t>4.50</t>
-        </is>
-      </c>
-      <c r="D210" t="inlineStr">
-        <is>
-          <t>5.75</t>
-        </is>
+      <c r="B210" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C210" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="D210" t="n">
+        <v>5.75</v>
       </c>
     </row>
     <row r="211">
@@ -3855,20 +3795,14 @@
           <t>QyLXA9qI</t>
         </is>
       </c>
-      <c r="B211" t="inlineStr">
-        <is>
-          <t>1.90</t>
-        </is>
-      </c>
-      <c r="C211" t="inlineStr">
-        <is>
-          <t>4.00</t>
-        </is>
-      </c>
-      <c r="D211" t="inlineStr">
-        <is>
-          <t>3.70</t>
-        </is>
+      <c r="B211" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C211" t="n">
+        <v>4</v>
+      </c>
+      <c r="D211" t="n">
+        <v>3.7</v>
       </c>
     </row>
     <row r="212">
@@ -3877,20 +3811,14 @@
           <t>Uoi8UUFe</t>
         </is>
       </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>1.91</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>3.90</t>
-        </is>
-      </c>
-      <c r="D212" t="inlineStr">
-        <is>
-          <t>3.60</t>
-        </is>
+      <c r="B212" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="C212" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D212" t="n">
+        <v>3.6</v>
       </c>
     </row>
     <row r="213">
@@ -3899,20 +3827,14 @@
           <t>tMfCTlV1</t>
         </is>
       </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>4.75</t>
-        </is>
-      </c>
-      <c r="D213" t="inlineStr">
-        <is>
-          <t>6.50</t>
-        </is>
+      <c r="B213" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="C213" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="D213" t="n">
+        <v>6.5</v>
       </c>
     </row>
     <row r="214">
@@ -3921,20 +3843,14 @@
           <t>Wzm5h1Tj</t>
         </is>
       </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>4.10</t>
-        </is>
-      </c>
-      <c r="D214" t="inlineStr">
-        <is>
-          <t>5.50</t>
-        </is>
+      <c r="B214" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C214" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D214" t="n">
+        <v>5.5</v>
       </c>
     </row>
     <row r="215">
@@ -3943,19 +3859,465 @@
           <t>M9cUJgca</t>
         </is>
       </c>
-      <c r="B215" t="inlineStr">
+      <c r="B215" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="C215" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="D215" t="n">
+        <v>3.05</v>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" s="1" t="inlineStr">
+        <is>
+          <t>lMloGBdO</t>
+        </is>
+      </c>
+      <c r="B216" t="n">
+        <v>1.57</v>
+      </c>
+      <c r="C216" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="D216" t="n">
+        <v>5.25</v>
+      </c>
+    </row>
+    <row r="217">
+      <c r="A217" s="1" t="inlineStr">
+        <is>
+          <t>fNexIXRB</t>
+        </is>
+      </c>
+      <c r="B217" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C217" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="D217" t="n">
+        <v>5.3</v>
+      </c>
+    </row>
+    <row r="218">
+      <c r="A218" s="1" t="inlineStr">
+        <is>
+          <t>00dYIDC5</t>
+        </is>
+      </c>
+      <c r="B218" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="C218" t="n">
+        <v>8</v>
+      </c>
+      <c r="D218" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="219">
+      <c r="A219" s="1" t="inlineStr">
+        <is>
+          <t>6catHisI</t>
+        </is>
+      </c>
+      <c r="B219" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="C219" t="n">
+        <v>3.45</v>
+      </c>
+      <c r="D219" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="A220" s="1" t="inlineStr">
+        <is>
+          <t>E3M7XCRb</t>
+        </is>
+      </c>
+      <c r="B220" t="n">
+        <v>2.65</v>
+      </c>
+      <c r="C220" t="n">
+        <v>3.35</v>
+      </c>
+      <c r="D220" t="n">
+        <v>2.45</v>
+      </c>
+    </row>
+    <row r="221">
+      <c r="A221" s="1" t="inlineStr">
+        <is>
+          <t>IyTbZYdn</t>
+        </is>
+      </c>
+      <c r="B221" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="C221" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="D221" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="222">
+      <c r="A222" s="1" t="inlineStr">
+        <is>
+          <t>SCmkFVBU</t>
+        </is>
+      </c>
+      <c r="B222" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="C222" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="D222" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="223">
+      <c r="A223" s="1" t="inlineStr">
+        <is>
+          <t>8QLBWWt5</t>
+        </is>
+      </c>
+      <c r="B223" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="C223" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="D223" t="n">
+        <v>6.1</v>
+      </c>
+    </row>
+    <row r="224">
+      <c r="A224" s="1" t="inlineStr">
+        <is>
+          <t>voUfzFst</t>
+        </is>
+      </c>
+      <c r="B224" t="n">
+        <v>3.05</v>
+      </c>
+      <c r="C224" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="D224" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="225">
+      <c r="A225" s="1" t="inlineStr">
+        <is>
+          <t>p0lFJwSk</t>
+        </is>
+      </c>
+      <c r="B225" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C225" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D225" t="inlineStr">
+        <is>
+          <t>3.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="226">
+      <c r="A226" s="1" t="inlineStr">
+        <is>
+          <t>vNmJIcsd</t>
+        </is>
+      </c>
+      <c r="B226" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C226" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D226" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="227">
+      <c r="A227" s="1" t="inlineStr">
+        <is>
+          <t>MHXbihN8</t>
+        </is>
+      </c>
+      <c r="B227" t="inlineStr">
         <is>
           <t>2.10</t>
         </is>
       </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>3.55</t>
-        </is>
-      </c>
-      <c r="D215" t="inlineStr">
-        <is>
-          <t>3.05</t>
+      <c r="C227" t="inlineStr">
+        <is>
+          <t>3.75</t>
+        </is>
+      </c>
+      <c r="D227" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="228">
+      <c r="A228" s="1" t="inlineStr">
+        <is>
+          <t>69kBKJCq</t>
+        </is>
+      </c>
+      <c r="B228" t="inlineStr">
+        <is>
+          <t>2.05</t>
+        </is>
+      </c>
+      <c r="C228" t="inlineStr">
+        <is>
+          <t>3.80</t>
+        </is>
+      </c>
+      <c r="D228" t="inlineStr">
+        <is>
+          <t>3.25</t>
+        </is>
+      </c>
+    </row>
+    <row r="229">
+      <c r="A229" s="1" t="inlineStr">
+        <is>
+          <t>h29zRLZF</t>
+        </is>
+      </c>
+      <c r="B229" t="inlineStr">
+        <is>
+          <t>2.38</t>
+        </is>
+      </c>
+      <c r="C229" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+      <c r="D229" t="inlineStr">
+        <is>
+          <t>3.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="230">
+      <c r="A230" s="1" t="inlineStr">
+        <is>
+          <t>QF7rPa4S</t>
+        </is>
+      </c>
+      <c r="B230" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C230" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+      <c r="D230" t="inlineStr">
+        <is>
+          <t>4.75</t>
+        </is>
+      </c>
+    </row>
+    <row r="231">
+      <c r="A231" s="1" t="inlineStr">
+        <is>
+          <t>nP8vQukM</t>
+        </is>
+      </c>
+      <c r="B231" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C231" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+      <c r="D231" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+    </row>
+    <row r="232">
+      <c r="A232" s="1" t="inlineStr">
+        <is>
+          <t>AszX60rp</t>
+        </is>
+      </c>
+      <c r="B232" t="inlineStr">
+        <is>
+          <t>2.75</t>
+        </is>
+      </c>
+      <c r="C232" t="inlineStr">
+        <is>
+          <t>4.20</t>
+        </is>
+      </c>
+      <c r="D232" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+    </row>
+    <row r="233">
+      <c r="A233" s="1" t="inlineStr">
+        <is>
+          <t>jix3jCxF</t>
+        </is>
+      </c>
+      <c r="B233" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="C233" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D233" t="inlineStr">
+        <is>
+          <t>2.90</t>
+        </is>
+      </c>
+    </row>
+    <row r="234">
+      <c r="A234" s="1" t="inlineStr">
+        <is>
+          <t>h6Py6Kcj</t>
+        </is>
+      </c>
+      <c r="B234" t="inlineStr">
+        <is>
+          <t>1.83</t>
+        </is>
+      </c>
+      <c r="C234" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D234" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="235">
+      <c r="A235" s="1" t="inlineStr">
+        <is>
+          <t>WdOu5vDd</t>
+        </is>
+      </c>
+      <c r="B235" t="inlineStr">
+        <is>
+          <t>2.15</t>
+        </is>
+      </c>
+      <c r="C235" t="inlineStr">
+        <is>
+          <t>3.40</t>
+        </is>
+      </c>
+      <c r="D235" t="inlineStr">
+        <is>
+          <t>3.30</t>
+        </is>
+      </c>
+    </row>
+    <row r="236">
+      <c r="A236" s="1" t="inlineStr">
+        <is>
+          <t>KCHNTNkc</t>
+        </is>
+      </c>
+      <c r="B236" t="inlineStr">
+        <is>
+          <t>1.80</t>
+        </is>
+      </c>
+      <c r="C236" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D236" t="inlineStr">
+        <is>
+          <t>4.00</t>
+        </is>
+      </c>
+    </row>
+    <row r="237">
+      <c r="A237" s="1" t="inlineStr">
+        <is>
+          <t>b3GRSs53</t>
+        </is>
+      </c>
+      <c r="B237" t="inlineStr">
+        <is>
+          <t>1.95</t>
+        </is>
+      </c>
+      <c r="C237" t="inlineStr">
+        <is>
+          <t>3.90</t>
+        </is>
+      </c>
+      <c r="D237" t="inlineStr">
+        <is>
+          <t>3.50</t>
+        </is>
+      </c>
+    </row>
+    <row r="238">
+      <c r="A238" s="1" t="inlineStr">
+        <is>
+          <t>tS5WR1K9</t>
+        </is>
+      </c>
+      <c r="B238" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
+      <c r="C238" t="inlineStr">
+        <is>
+          <t>4.33</t>
+        </is>
+      </c>
+      <c r="D238" t="inlineStr">
+        <is>
+          <t>5.25</t>
         </is>
       </c>
     </row>
